--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI14"/>
+  <dimension ref="A1:BI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46156.41666666666</v>
+        <v>46156.38541666666</v>
       </c>
     </row>
     <row r="5">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46156.5</v>
+        <v>46156.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46156.58333333334</v>
+        <v>46156.46180555555</v>
       </c>
     </row>
     <row r="7">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46156.6875</v>
+        <v>46156.47916666666</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.47916666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.48958333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,6 +3300,6113 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>St. Pölten</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>WSPG Wels</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Austria Wien II</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kapfenberger SV</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mekelakeya</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Negele Arsi Ketema</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sturm Graz II</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rapid Wien II</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="3" t="n">
+        <v>46156.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Smail</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sohar</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
+        <v>46156.51388888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="3" t="n">
+        <v>46156.53819444445</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al-Nahda</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Al Seeb</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
+        <v>46156.56597222222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>46156.58333333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia 1929</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beroe</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46156.59375</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>46156.625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
+        <v>46156.625</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
+        <v>46156.625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bradford City</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
+        <v>46156.66666666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
+        <v>46156.6875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3" t="n">
+        <v>46156.79166666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Qarabağ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mil Mugan FK</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Neftçi</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Zira</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sumqayıt</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Karvan FK</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Qabala</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Araz</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kapaz</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>İnter Bakı</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Turan</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI45"/>
+  <dimension ref="A1:BI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46156.51388888889</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46156.53819444445</v>
+        <v>46156.51388888889</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46156.56597222222</v>
+        <v>46156.53819444445</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46156.58333333334</v>
+        <v>46156.56597222222</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46156.59375</v>
+        <v>46156.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.59375</v>
       </c>
     </row>
     <row r="26">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46156.66666666666</v>
+        <v>46156.625</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46156.6875</v>
+        <v>46156.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46156.79166666666</v>
+        <v>46156.6875</v>
       </c>
     </row>
     <row r="31">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,6 +9407,203 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Zira</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sumqayıt</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
         <v>2.92</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.06</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>3.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="R14" t="n">
-        <v>3.27</v>
+        <v>4.24</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>3.36</v>
       </c>
       <c r="R15" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="R18" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="R14" t="n">
-        <v>4.24</v>
+        <v>3.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="R18" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>4.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>2.92</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="R15" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.75</v>
+        <v>4.24</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>4.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>3.22</v>
+        <v>1.75</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>2.96</v>
+        <v>4.09</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>3.92</v>
       </c>
       <c r="R13" t="n">
-        <v>3.22</v>
+        <v>4.24</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="R16" t="n">
-        <v>4.09</v>
+        <v>2.96</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI46"/>
+  <dimension ref="A1:BI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.36</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>4.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>3.22</v>
+        <v>1.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46156.51388888889</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46156.53819444445</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46156.56597222222</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46156.58333333334</v>
+        <v>46156.51388888889</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46156.59375</v>
+        <v>46156.53819444445</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.56597222222</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.59375</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46156.66666666666</v>
+        <v>46156.625</v>
       </c>
     </row>
     <row r="30">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46156.6875</v>
+        <v>46156.625</v>
       </c>
     </row>
     <row r="31">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46156.79166666666</v>
+        <v>46156.625</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.6875</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9604,6 +9604,597 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3" t="n">
+        <v>46156.875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Qarabağ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mil Mugan FK</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="R13" t="n">
-        <v>4.24</v>
+        <v>3.27</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>4.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>3.22</v>
+        <v>1.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="R17" t="n">
-        <v>3.27</v>
+        <v>4.24</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.75</v>
+        <v>4.09</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>4.09</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
         <v>2.92</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>2.92</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="R14" t="n">
-        <v>4.09</v>
+        <v>4.24</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>3.44</v>
       </c>
       <c r="R15" t="n">
-        <v>3.22</v>
+        <v>4.09</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="R12" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.57</v>
+        <v>3.92</v>
       </c>
       <c r="R18" t="n">
-        <v>3.22</v>
+        <v>4.24</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.75</v>
+        <v>4.09</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="R12" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>3.27</v>
+        <v>4.47</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="R14" t="n">
-        <v>2.96</v>
+        <v>4.09</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="R15" t="n">
-        <v>4.24</v>
+        <v>3.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="R19" t="n">
-        <v>4.09</v>
+        <v>4.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>3.27</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>4.47</v>
+        <v>4.09</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.06</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>3.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="R22" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>3.22</v>
+        <v>4.47</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
         <v>2.92</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>2.92</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.57</v>
+        <v>3.36</v>
       </c>
       <c r="R22" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="R23" t="n">
-        <v>4.47</v>
+        <v>4.09</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1810,55 +1810,55 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.8</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2204,55 +2204,55 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,52 +2261,52 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>3.22</v>
+        <v>4.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>4.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>4.24</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.06</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.75</v>
+        <v>2.96</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
       <c r="R23" t="n">
-        <v>4.09</v>
+        <v>3.27</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1795,70 +1795,70 @@
         <v>2.92</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X7" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>2.43</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
         <v>1.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
         <v>1.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="R8" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>2.45</v>
@@ -1998,64 +1998,64 @@
         <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>2.55</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
         <v>1.57</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.8</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
         <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
         <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>2.28</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
         <v>3.25</v>
@@ -2386,124 +2386,124 @@
         <v>4.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AM13" t="n">
         <v>1.25</v>
       </c>
       <c r="AN13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.17</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.06</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>4.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.96</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5341,124 +5341,124 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>3.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.5</v>
+        <v>3.66</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>10.89</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.3</v>
       </c>
-      <c r="W7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AK7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
       <c r="BE7" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.8</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.2</v>
       </c>
-      <c r="W9" t="n">
+      <c r="BC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4</v>
       </c>
-      <c r="X9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="BE9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.37</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.42</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.9</v>
       </c>
-      <c r="R21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>4.09</v>
+        <v>4.6</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN22" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.66</v>
+        <v>6.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>3.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="R30" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="X31" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.8</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>4.05</v>
       </c>
       <c r="AE31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AN31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF31" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G48" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.8</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.2</v>
       </c>
-      <c r="W7" t="n">
+      <c r="BC7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4</v>
       </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="BE7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.37</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.3</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AK9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BD9" t="n">
         <v>5.5</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,34 +3559,34 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
         <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
         <v>5.6</v>
@@ -3595,97 +3595,97 @@
         <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>4.6</v>
+        <v>1.68</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
         <v>4.6</v>
       </c>
       <c r="S22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
         <v>4.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="X22" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.42</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR23" t="n">
         <v>1.68</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>3.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="R31" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="S31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
         <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
         <v>4</v>
@@ -2031,16 +2031,16 @@
         <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.3</v>
@@ -2055,7 +2055,7 @@
         <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,34 +2180,34 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V9" t="n">
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X9" t="n">
         <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
         <v>4</v>
@@ -2228,16 +2228,16 @@
         <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
         <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.3</v>
@@ -2252,7 +2252,7 @@
         <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,52 +2261,52 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AS9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AT9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AY9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.42</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
         <v>1.68</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5347,13 +5347,13 @@
         <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="X25" t="n">
         <v>2.17</v>
@@ -5362,25 +5362,25 @@
         <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AG25" t="n">
         <v>2.2</v>
@@ -5395,16 +5395,16 @@
         <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,52 +5413,52 @@
         <v>1.11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AT25" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AU25" t="n">
         <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BA25" t="n">
         <v>3.45</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="X29" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.8</v>
+        <v>6.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4.05</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AN29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="R30" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W30" t="n">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="X30" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>3.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.05</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
         <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AS30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE30" t="n">
         <v>2.36</v>
       </c>
-      <c r="AT30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF30" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="R31" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1213,10 +1213,10 @@
         <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="X4" t="n">
         <v>3.28</v>
@@ -1231,7 +1231,7 @@
         <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
         <v>1.44</v>
@@ -1240,16 +1240,16 @@
         <v>2.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
         <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
         <v>1.1</v>
@@ -1795,7 +1795,7 @@
         <v>2.92</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
         <v>2.3</v>
@@ -1804,49 +1804,49 @@
         <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
         <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="AE7" t="n">
         <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
         <v>1.62</v>
@@ -1903,13 +1903,13 @@
         <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BD7" t="n">
         <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BF7" t="n">
         <v>1.2</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,40 +1983,40 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>3.21</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
@@ -2028,34 +2028,34 @@
         <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,67 +2180,67 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
         <v>1.36</v>
@@ -2249,10 +2249,10 @@
         <v>2.9</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,49 +2261,49 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="BB9" t="n">
         <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF9" t="n">
         <v>1.36</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
         <v>3.25</v>
@@ -2386,70 +2386,70 @@
         <v>4.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
         <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="X10" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
         <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
         <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="n">
         <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>1.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
@@ -2503,7 +2503,7 @@
         <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,80 +2968,80 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
         <v>4.6</v>
       </c>
       <c r="S13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN13" t="n">
         <v>2.05</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>4.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>1.67</v>
       </c>
       <c r="S19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI22" t="n">
         <v>4.8</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AM22" t="n">
         <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5726,22 +5726,22 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S27" t="n">
         <v>2.79</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="V27" t="n">
         <v>1.4</v>
@@ -5756,37 +5756,37 @@
         <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
         <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
         <v>1.73</v>
@@ -5795,7 +5795,7 @@
         <v>2.06</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
         <v>1.67</v>
@@ -5804,55 +5804,55 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="BB27" t="n">
         <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
         <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
         <v>2.3</v>
@@ -5944,16 +5944,16 @@
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="X28" t="n">
         <v>2.65</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
         <v>1.07</v>
@@ -5962,28 +5962,28 @@
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI28" t="n">
         <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK28" t="n">
         <v>1.75</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="R29" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="S29" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.3</v>
       </c>
-      <c r="U29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.57</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.75</v>
+        <v>1.49</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX31" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AY31" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.49</v>
+        <v>2.98</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
         <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6717,16 +6717,16 @@
         <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
         <v>1.36</v>
@@ -6735,10 +6735,10 @@
         <v>2.89</v>
       </c>
       <c r="X32" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
         <v>6.1</v>
@@ -6747,10 +6747,10 @@
         <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD32" t="n">
         <v>3.8</v>
@@ -6762,67 +6762,67 @@
         <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" t="n">
-        <v>5.15</v>
+        <v>4.7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY32" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="BB32" t="n">
         <v>1.2</v>
@@ -6837,7 +6837,7 @@
         <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6908,109 +6908,109 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="R33" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
       <c r="S33" t="n">
         <v>1.57</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U33" t="n">
         <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W33" t="n">
         <v>4.2</v>
       </c>
       <c r="X33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
         <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AF33" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AN33" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AY33" t="n">
         <v>1.36</v>
@@ -7019,16 +7019,16 @@
         <v>1.16</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BD33" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BE33" t="n">
         <v>2.2</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
         <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.29</v>
+        <v>5.75</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AL7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
         <v>2.6</v>
       </c>
       <c r="T9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.75</v>
+        <v>4.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.85</v>
+        <v>2.13</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.19</v>
+        <v>5.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,52 +2261,52 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>4.09</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.3</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AN20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD20" t="n">
         <v>3.25</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="BE20" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.65</v>
+        <v>1.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.79</v>
+        <v>6.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.87</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="T29" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="X29" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.19</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AR29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS29" t="n">
         <v>1.61</v>
       </c>
-      <c r="AS29" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AT29" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AW29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AX29" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AY29" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>1.15</v>
       </c>
       <c r="BA29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC29" t="n">
         <v>1.49</v>
       </c>
-      <c r="BB29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD29" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BB30" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>10</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="BC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.42</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="R31" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U31" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="X31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AQ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA31" t="n">
         <v>1.49</v>
       </c>
-      <c r="AR31" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC31" t="n">
         <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1213,55 +1213,55 @@
         <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
@@ -1309,19 +1309,19 @@
         <v>3.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>2.6</v>
       </c>
       <c r="T7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.17</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
         <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>3.21</v>
+        <v>2.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="X9" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD9" t="n">
         <v>6</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="S10" t="n">
         <v>2.22</v>
@@ -2401,7 +2401,7 @@
         <v>2.81</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="Y10" t="n">
         <v>1.39</v>
@@ -2416,10 +2416,10 @@
         <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.93</v>
@@ -2446,7 +2446,7 @@
         <v>1.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
         <v>1.94</v>
@@ -2503,7 +2503,7 @@
         <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.42</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX17" t="n">
         <v>1.66</v>
       </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>4.09</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.3</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AN18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.25</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="BE18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>4.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5726,34 +5726,34 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="S27" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="U27" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="X27" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
         <v>6.5</v>
@@ -5771,19 +5771,19 @@
         <v>3.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
         <v>3.04</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.11</v>
@@ -5792,10 +5792,10 @@
         <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AN27" t="n">
         <v>1.67</v>
@@ -5804,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.44</v>
@@ -5837,13 +5837,13 @@
         <v>1.73</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BB27" t="n">
         <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD27" t="n">
         <v>3.8</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
         <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="S28" t="n">
         <v>2.3</v>
@@ -5938,52 +5938,52 @@
         <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="X28" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
         <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD28" t="n">
         <v>3.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI28" t="n">
         <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
         <v>1.75</v>
@@ -5992,61 +5992,61 @@
         <v>1.95</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
         <v>3.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BF28" t="n">
         <v>1.17</v>
@@ -6332,28 +6332,28 @@
         <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
         <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="X30" t="n">
         <v>2.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
         <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
         <v>1.19</v>
@@ -6365,10 +6365,10 @@
         <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
@@ -6377,13 +6377,13 @@
         <v>4.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK30" t="n">
         <v>1.58</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AM30" t="n">
         <v>1.3</v>
@@ -6908,19 +6908,19 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="R33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S33" t="n">
         <v>1.57</v>
       </c>
       <c r="T33" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="U33" t="n">
         <v>8</v>
@@ -6929,19 +6929,19 @@
         <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X33" t="n">
         <v>2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
         <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
@@ -6950,19 +6950,19 @@
         <v>1.06</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AG33" t="n">
         <v>2.01</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AI33" t="n">
         <v>3.1</v>
@@ -6971,10 +6971,10 @@
         <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
         <v>1.02</v>
@@ -7013,13 +7013,13 @@
         <v>1.68</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="BB33" t="n">
         <v>1.13</v>
@@ -7034,7 +7034,7 @@
         <v>2.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1234,16 +1234,16 @@
         <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
         <v>2.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
         <v>4</v>
@@ -1315,10 +1315,10 @@
         <v>2.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
         <v>1.13</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD7" t="n">
         <v>6</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR7" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
         <v>2.6</v>
@@ -2013,7 +2013,7 @@
         <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
         <v>1.17</v>
@@ -2022,16 +2022,16 @@
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AG8" t="n">
         <v>2</v>
@@ -2043,7 +2043,7 @@
         <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
         <v>1.36</v>
@@ -2103,7 +2103,7 @@
         <v>1.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
         <v>2.2</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.76</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
         <v>4.33</v>
@@ -2389,7 +2389,7 @@
         <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
         <v>5</v>
@@ -2431,7 +2431,7 @@
         <v>3.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
         <v>6.5</v>
@@ -2446,10 +2446,10 @@
         <v>1.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="V17" t="n">
         <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.42</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.06</v>
+        <v>3.53</v>
       </c>
       <c r="R21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.67</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AL21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX21" t="n">
         <v>1.66</v>
       </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
         <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.21</v>
@@ -5356,31 +5356,31 @@
         <v>3.58</v>
       </c>
       <c r="X25" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
         <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="AG25" t="n">
         <v>2.2</v>
@@ -5401,43 +5401,43 @@
         <v>2.2</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AZ25" t="n">
         <v>1.37</v>
@@ -5446,19 +5446,19 @@
         <v>3.45</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5735,13 +5735,13 @@
         <v>2.93</v>
       </c>
       <c r="S27" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5768,10 +5768,10 @@
         <v>1.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
         <v>1.93</v>
@@ -5804,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.44</v>
@@ -5819,7 +5819,7 @@
         <v>2.97</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV27" t="n">
         <v>2.51</v>
@@ -5843,7 +5843,7 @@
         <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
         <v>3.8</v>
@@ -5923,22 +5923,22 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
         <v>3.7</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
         <v>1.36</v>
@@ -5947,10 +5947,10 @@
         <v>2.75</v>
       </c>
       <c r="X28" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z28" t="n">
         <v>7</v>
@@ -5965,19 +5965,19 @@
         <v>1.29</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" t="n">
         <v>6</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>3.06</v>
       </c>
       <c r="S29" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="X29" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.84</v>
+        <v>6.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AN29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT29" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH29" t="n">
+      <c r="AU29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.85</v>
       </c>
-      <c r="AI29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="BF29" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.42</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>6.76</v>
       </c>
       <c r="R30" t="n">
-        <v>3.1</v>
+        <v>10.6</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W30" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="X30" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN30" t="n">
         <v>4</v>
       </c>
-      <c r="AE30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX30" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG30" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ30" t="n">
+      <c r="AY30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BA30" t="n">
-        <v>2.98</v>
+        <v>6.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="R31" t="n">
         <v>1.87</v>
@@ -6526,10 +6526,10 @@
         <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V31" t="n">
         <v>1.27</v>
@@ -6550,40 +6550,40 @@
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
         <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL31" t="n">
         <v>2.5</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
         <v>1.25</v>
@@ -6628,19 +6628,19 @@
         <v>1.49</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BC31" t="n">
         <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
         <v>1.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6908,19 +6908,19 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="R33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="U33" t="n">
         <v>8</v>
@@ -6929,19 +6929,19 @@
         <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X33" t="n">
         <v>2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
         <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
@@ -6953,22 +6953,22 @@
         <v>6.05</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK33" t="n">
         <v>1.77</v>
@@ -6977,10 +6977,10 @@
         <v>2</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>7.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1213,49 +1213,49 @@
         <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="X4" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
         <v>1.95</v>
@@ -1312,16 +1312,16 @@
         <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="X8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,49 +2064,49 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF8" t="n">
         <v>1.36</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="X9" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2</v>
       </c>
-      <c r="AG9" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.97</v>
+        <v>4.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
         <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
         <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
         <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>5.08</v>
+        <v>3.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AA21" t="n">
         <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5374,16 +5374,16 @@
         <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH25" t="n">
         <v>1.57</v>
@@ -5783,7 +5783,7 @@
         <v>1.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.11</v>
@@ -5795,10 +5795,10 @@
         <v>2.04</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>1.3</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BA27" t="n">
         <v>2.15</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>1.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="R29" t="n">
-        <v>3.06</v>
+        <v>10.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="X29" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN29" t="n">
         <v>4</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ29" t="n">
+      <c r="AY29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BA29" t="n">
-        <v>2.98</v>
+        <v>6.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="R30" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="AD30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.57</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AL30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE30" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ30" t="n">
+      <c r="BF30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.67</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y31" t="n">
         <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
         <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AH31" t="n">
         <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.25</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ31" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.49</v>
+        <v>2.96</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD31" t="n">
         <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF31" t="n">
         <v>1.22</v>
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="S32" t="n">
         <v>2.7</v>
@@ -6756,7 +6756,7 @@
         <v>3.8</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
         <v>2</v>
@@ -6768,7 +6768,7 @@
         <v>1.36</v>
       </c>
       <c r="AI32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.14</v>
@@ -6780,7 +6780,7 @@
         <v>2.2</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN32" t="n">
         <v>1.53</v>
@@ -6792,13 +6792,13 @@
         <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
         <v>1.78</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AT32" t="n">
         <v>2.97</v>
@@ -6807,13 +6807,13 @@
         <v>3.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AY32" t="n">
         <v>1.3</v>
@@ -6837,7 +6837,7 @@
         <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6986,34 +6986,34 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
         <v>1.77</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AZ33" t="n">
         <v>1.11</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR7" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,49 +2064,49 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
         <v>1.36</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="U9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.8</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2</v>
-      </c>
       <c r="AH9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R16" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U16" t="n">
         <v>3.9</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="X16" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN16" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
         <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>10.4</v>
+        <v>3.1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="X29" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.93</v>
+        <v>4.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AK29" t="n">
         <v>1.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.67</v>
+        <v>1.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.77</v>
+        <v>6.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.87</v>
+        <v>10.4</v>
       </c>
       <c r="S30" t="n">
-        <v>4.05</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W30" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="X30" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU30" t="n">
         <v>5</v>
       </c>
-      <c r="AA30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK30" t="n">
+      <c r="AV30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ30" t="n">
+      <c r="BD30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>3.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="R31" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.25</v>
       </c>
-      <c r="U31" t="n">
-        <v>3.7</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y31" t="n">
         <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
         <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="n">
         <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AQ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA31" t="n">
         <v>1.49</v>
       </c>
-      <c r="AR31" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
         <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF31" t="n">
         <v>1.22</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI49"/>
+  <dimension ref="A1:BI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,124 +2574,124 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="X11" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
         <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
         <v>4.45</v>
       </c>
       <c r="AJ11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BD11" t="n">
         <v>4.2</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>4.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.53</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL16" t="n">
         <v>2.15</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.41</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>3.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="R23" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG23" t="n">
         <v>4</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="AD30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.57</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AL30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE30" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ30" t="n">
+      <c r="BF30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.67</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.77</v>
+        <v>6.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.87</v>
+        <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>4.05</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU31" t="n">
         <v>5</v>
       </c>
-      <c r="AA31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
+      <c r="AV31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC31" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="BD31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,794 +9407,6 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Oued Akbou</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI47" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Qarabağ</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mil Mugan FK</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI49" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1219,10 +1219,10 @@
         <v>2.62</v>
       </c>
       <c r="X4" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
         <v>8</v>
@@ -1240,10 +1240,10 @@
         <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
         <v>3.7</v>
@@ -1264,10 +1264,10 @@
         <v>1.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BD4" t="n">
         <v>3.3</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
         <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>2.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,49 +1867,49 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="BB7" t="n">
         <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF7" t="n">
         <v>1.36</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="U8" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2</v>
-      </c>
       <c r="AH8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="X9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,40 +2377,40 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
         <v>4.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
         <v>5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="X10" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
         <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
         <v>1.05</v>
@@ -2422,13 +2422,13 @@
         <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
         <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AH10" t="n">
         <v>1.24</v>
@@ -2440,7 +2440,7 @@
         <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL10" t="n">
         <v>1.91</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
         <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
         <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>2.19</v>
       </c>
       <c r="T22" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
         <v>5.08</v>
@@ -4777,7 +4777,7 @@
         <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
         <v>1.22</v>
@@ -4858,7 +4858,7 @@
         <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BD22" t="n">
         <v>4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5374,16 +5374,16 @@
         <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
         <v>1.57</v>
@@ -5395,10 +5395,10 @@
         <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AM25" t="n">
         <v>1.17</v>
@@ -5923,34 +5923,34 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>4.76</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="X28" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
         <v>7</v>
@@ -5962,7 +5962,7 @@
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD28" t="n">
         <v>3.4</v>
@@ -5971,10 +5971,10 @@
         <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -5992,10 +5992,10 @@
         <v>1.95</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
         <v>3.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
         <v>1.17</v>
@@ -6326,7 +6326,7 @@
         <v>1.87</v>
       </c>
       <c r="S30" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
         <v>2.4</v>
@@ -6368,7 +6368,7 @@
         <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
@@ -6386,10 +6386,10 @@
         <v>2.5</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.84</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
         <v>1.37</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL31" t="n">
         <v>2.05</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI45"/>
+  <dimension ref="A1:BI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
       <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM8" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR8" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,70 +2180,70 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>2.9</v>
@@ -2252,7 +2252,7 @@
         <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,49 +2261,49 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="BB9" t="n">
         <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF9" t="n">
         <v>1.36</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD14" t="n">
         <v>3.5</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF16" t="n">
         <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="R18" t="n">
         <v>4.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>4.8</v>
+        <v>5.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.9</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.9</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AE20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI20" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AN20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD20" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46156.51388888889</v>
+        <v>46156.5</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5341,124 +5341,124 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46156.53819444445</v>
+        <v>46156.51388888889</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5538,124 +5538,124 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46156.56597222222</v>
+        <v>46156.53819444445</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46156.58333333334</v>
+        <v>46156.56597222222</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,58 +5923,58 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="S28" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="X28" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -5986,70 +5986,70 @@
         <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AW28" t="n">
         <v>1.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC28" t="n">
         <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46156.59375</v>
+        <v>46156.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
         <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T29" t="n">
         <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>3.7</v>
+        <v>4.76</v>
       </c>
       <c r="V29" t="n">
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="X29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV29" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="AW29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BD29" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46156.625</v>
+        <v>46156.59375</v>
       </c>
     </row>
     <row r="30">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.8</v>
+        <v>3.72</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>3.06</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
         <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AN31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT31" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AU31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="AI31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="BF31" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,134 +6711,134 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.51</v>
+        <v>6.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.63</v>
+        <v>10.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="W32" t="n">
-        <v>2.89</v>
+        <v>4.4</v>
       </c>
       <c r="X32" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AB32" t="n">
         <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BG32" t="n">
         <v>0</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46156.66666666666</v>
+        <v>46156.625</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>9.800000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK33" t="n">
         <v>1.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U33" t="n">
-        <v>8</v>
-      </c>
-      <c r="V33" t="n">
+      <c r="AL33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB33" t="n">
         <v>1.2</v>
       </c>
-      <c r="W33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH33" t="n">
+      <c r="BC33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE33" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF33" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46156.6875</v>
+        <v>46156.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46156.79166666666</v>
+        <v>46156.6875</v>
       </c>
     </row>
     <row r="35">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.79166666666</v>
       </c>
     </row>
     <row r="36">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,991 +8422,6 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Qarabağ</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mil Mugan FK</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Zira</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Sumqayıt</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Karvan FK</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Qabala</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI45" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,70 +1983,70 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>2.9</v>
@@ -2055,7 +2055,7 @@
         <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,49 +2064,49 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AS8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
         <v>1.36</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,70 +2180,70 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
         <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="X9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
         <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL9" t="n">
         <v>2.9</v>
@@ -2252,7 +2252,7 @@
         <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,49 +2261,49 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AS9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AT9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AY9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
         <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF9" t="n">
         <v>1.36</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="Q12" t="n">
         <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3168,13 +3168,13 @@
         <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
         <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="T14" t="n">
         <v>2.2</v>
@@ -3207,10 +3207,10 @@
         <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
         <v>1.8</v>
@@ -3219,7 +3219,7 @@
         <v>3.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
         <v>6.45</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.69</v>
+        <v>3.35</v>
       </c>
       <c r="X20" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AN20" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.72</v>
+        <v>6.8</v>
       </c>
       <c r="R31" t="n">
-        <v>3.06</v>
+        <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="X31" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB31" t="n">
         <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN31" t="n">
         <v>4</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG31" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AY31" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.71</v>
+        <v>1.15</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.83</v>
+        <v>6.1</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.8</v>
+        <v>3.72</v>
       </c>
       <c r="R32" t="n">
-        <v>10.4</v>
+        <v>3.06</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="X32" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
         <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AD32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM32" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AN32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT32" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="AU32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.85</v>
       </c>
-      <c r="AI32" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ32" t="n">
+      <c r="BF32" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
         <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>5.08</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA19" t="n">
         <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="V20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.25</v>
       </c>
-      <c r="W20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="BC20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
         <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W23" t="n">
         <v>3.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.16</v>
       </c>
       <c r="X23" t="n">
         <v>2.39</v>
@@ -4968,31 +4968,31 @@
         <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
         <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" t="n">
         <v>4.6</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.8</v>
+        <v>3.72</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>3.06</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
         <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AN31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT31" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AU31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="AI31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="BF31" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.72</v>
+        <v>6.8</v>
       </c>
       <c r="R32" t="n">
-        <v>3.06</v>
+        <v>10.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W32" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="X32" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB32" t="n">
         <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN32" t="n">
         <v>4</v>
       </c>
-      <c r="AE32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF32" t="n">
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX32" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AY32" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.71</v>
+        <v>1.15</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.83</v>
+        <v>6.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="R4" t="n">
-        <v>4.88</v>
+        <v>4.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>5.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>3.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2</v>
-      </c>
       <c r="AH8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2377,37 +2377,37 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
         <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="X10" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" t="n">
         <v>1.04</v>
@@ -2416,22 +2416,22 @@
         <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD10" t="n">
         <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI10" t="n">
         <v>6.5</v>
@@ -2440,7 +2440,7 @@
         <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>1.91</v>
@@ -2503,7 +2503,7 @@
         <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>5.75</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
         <v>1.27</v>
@@ -4174,16 +4174,16 @@
         <v>3.35</v>
       </c>
       <c r="X19" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
@@ -4195,10 +4195,10 @@
         <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
         <v>2.5</v>
@@ -4207,73 +4207,73 @@
         <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC19" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
         <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF19" t="n">
         <v>1.22</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AN24" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BF24" t="n">
         <v>1.13</v>
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S26" t="n">
         <v>1.91</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="U26" t="n">
         <v>4.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="X26" t="n">
         <v>2.13</v>
@@ -5559,7 +5559,7 @@
         <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA26" t="n">
         <v>1.13</v>
@@ -5574,10 +5574,10 @@
         <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AG26" t="n">
         <v>2.2</v>
@@ -5592,10 +5592,10 @@
         <v>1.22</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AM26" t="n">
         <v>1.17</v>
@@ -5607,40 +5607,40 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BB26" t="n">
         <v>1.15</v>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R29" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="S29" t="n">
         <v>2.2</v>
@@ -6144,19 +6144,19 @@
         <v>2.98</v>
       </c>
       <c r="X29" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="Y29" t="n">
         <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
         <v>1.25</v>
@@ -6168,7 +6168,7 @@
         <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
         <v>3.2</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,130 +6317,130 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.67</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="R30" t="n">
-        <v>1.87</v>
+        <v>3.06</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="U30" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X30" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Y30" t="n">
         <v>1.51</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
         <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AD30" t="n">
         <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.17</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.25</v>
       </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.49</v>
+        <v>2.83</v>
       </c>
       <c r="BB30" t="n">
         <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="BD30" t="n">
         <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF30" t="n">
         <v>1.22</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="R31" t="n">
-        <v>3.06</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="X31" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
         <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AD31" t="n">
         <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="AH31" t="n">
         <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.85</v>
+        <v>4.34</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AQ31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA31" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.83</v>
       </c>
       <c r="BB31" t="n">
         <v>1.18</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
         <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF31" t="n">
         <v>1.22</v>
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S32" t="n">
         <v>1.57</v>
@@ -6726,22 +6726,22 @@
         <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="V32" t="n">
         <v>1.14</v>
       </c>
       <c r="W32" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="X32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA32" t="n">
         <v>1.18</v>
@@ -6759,7 +6759,7 @@
         <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AG32" t="n">
         <v>1.8</v>
@@ -6768,10 +6768,10 @@
         <v>1.85</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
         <v>1.67</v>
@@ -6816,7 +6816,7 @@
         <v>2.1</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AZ32" t="n">
         <v>1.15</v>
@@ -6831,7 +6831,7 @@
         <v>1.57</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE32" t="n">
         <v>2.2</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1213,19 +1213,19 @@
         <v>5.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA4" t="n">
         <v>1.05</v>
@@ -1264,7 +1264,7 @@
         <v>1.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
         <v>1.94</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.5</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
       <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM8" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE8" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>4.05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
         <v>2.2</v>
@@ -2395,10 +2395,10 @@
         <v>5.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="X10" t="n">
         <v>2.81</v>
@@ -2407,7 +2407,7 @@
         <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AA10" t="n">
         <v>1.04</v>
@@ -2434,7 +2434,7 @@
         <v>1.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.1</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>4.75</v>
+        <v>2.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="X14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.79</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM14" t="n">
         <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R19" t="n">
         <v>4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
         <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="R21" t="n">
         <v>4.2</v>
       </c>
       <c r="S21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.05</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AG21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.25</v>
       </c>
-      <c r="W21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM21" t="n">
+      <c r="AN21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
         <v>2.81</v>
@@ -5953,7 +5953,7 @@
         <v>1.43</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="AA28" t="n">
         <v>1.08</v>
@@ -5962,25 +5962,25 @@
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.11</v>
@@ -5989,7 +5989,7 @@
         <v>1.73</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AM28" t="n">
         <v>1.33</v>
@@ -6001,55 +6001,55 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC28" t="n">
         <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="BE28" t="n">
         <v>1.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="V29" t="n">
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="X29" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" t="n">
         <v>1.06</v>
@@ -6162,25 +6162,25 @@
         <v>1.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
         <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
         <v>1.75</v>
@@ -6234,19 +6234,19 @@
         <v>3.55</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
         <v>3.06</v>
@@ -6329,7 +6329,7 @@
         <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
         <v>3.5</v>
@@ -6341,10 +6341,10 @@
         <v>3.3</v>
       </c>
       <c r="X30" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
         <v>6.05</v>
@@ -6353,7 +6353,7 @@
         <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC30" t="n">
         <v>1.19</v>
@@ -6368,13 +6368,13 @@
         <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.17</v>
@@ -6386,49 +6386,49 @@
         <v>2.3</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.49</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="BB30" t="n">
         <v>1.18</v>
@@ -6440,10 +6440,10 @@
         <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>7.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV31" t="n">
         <v>3.6</v>
       </c>
-      <c r="X31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
+      <c r="AW31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC31" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="BD31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE31" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BF31" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>3.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="R32" t="n">
-        <v>10.3</v>
+        <v>1.88</v>
       </c>
       <c r="S32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.57</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="AL32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG32" t="n">
+      <c r="BC32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AH32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ32" t="n">
+      <c r="BF32" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6911,10 +6911,10 @@
         <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S33" t="n">
         <v>2.7</v>
@@ -6932,13 +6932,13 @@
         <v>2.89</v>
       </c>
       <c r="X33" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA33" t="n">
         <v>1.06</v>
@@ -6947,16 +6947,16 @@
         <v>1.04</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD33" t="n">
         <v>3.8</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
         <v>2.88</v>
@@ -6986,31 +6986,31 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AR33" t="n">
         <v>1.78</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="AT33" t="n">
         <v>2.97</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AY33" t="n">
         <v>1.3</v>
@@ -7022,10 +7022,10 @@
         <v>2.38</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BD33" t="n">
         <v>4</v>
@@ -7108,19 +7108,19 @@
         <v>1.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.21</v>
+        <v>6.3</v>
       </c>
       <c r="R34" t="n">
-        <v>9.369999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S34" t="n">
         <v>1.57</v>
       </c>
       <c r="T34" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="V34" t="n">
         <v>1.21</v>
@@ -7129,16 +7129,16 @@
         <v>4.2</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB34" t="n">
         <v>1.01</v>
@@ -7147,79 +7147,79 @@
         <v>1.11</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="n">
         <v>1.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL34" t="n">
         <v>2.05</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.84</v>
+        <v>3.07</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.5</v>
+        <v>14.25</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC34" t="n">
         <v>1.7</v>
@@ -7228,7 +7228,7 @@
         <v>5</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BF34" t="n">
         <v>1.33</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T7" t="n">
         <v>2.3</v>
@@ -1816,7 +1816,7 @@
         <v>1.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
         <v>1.07</v>
@@ -1825,16 +1825,16 @@
         <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
         <v>3.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
         <v>2.8</v>
@@ -1894,13 +1894,13 @@
         <v>1.41</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
         <v>1.95</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
         <v>2.7</v>
@@ -2001,13 +2001,13 @@
         <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
         <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.74</v>
@@ -2031,10 +2031,10 @@
         <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
@@ -2049,7 +2049,7 @@
         <v>1.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AM8" t="n">
         <v>1.25</v>
@@ -2091,16 +2091,16 @@
         <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BD8" t="n">
         <v>5.5</v>
@@ -2180,19 +2180,19 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="R9" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
         <v>3.1</v>
@@ -2210,10 +2210,10 @@
         <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
@@ -2228,7 +2228,7 @@
         <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AG9" t="n">
         <v>1.95</v>
@@ -2237,13 +2237,13 @@
         <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>2.9</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="AG11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT11" t="n">
         <v>2.63</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AU11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="S22" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL22" t="n">
         <v>2.2</v>
       </c>
-      <c r="U22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AM22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.99</v>
+        <v>1.2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,80 +4938,80 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="W23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.91</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5547,10 +5547,10 @@
         <v>4.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="X26" t="n">
         <v>2.13</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.28</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="R31" t="n">
-        <v>10.3</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.57</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="AL31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="BC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.8</v>
       </c>
-      <c r="AH31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="BF31" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.88</v>
+        <v>7.9</v>
       </c>
       <c r="S32" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>2.25</v>
+        <v>7.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" t="n">
         <v>3.6</v>
       </c>
-      <c r="X32" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK32" t="n">
+      <c r="AW32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC32" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="BD32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE32" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BF32" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1204,34 +1204,34 @@
         <v>4.25</v>
       </c>
       <c r="S4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.15</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U4" t="n">
-        <v>5.61</v>
+        <v>4.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X4" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
@@ -1240,34 +1240,34 @@
         <v>3.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.87</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AS7" t="n">
         <v>2.05</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,64 +1983,64 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>3.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD8" t="n">
         <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="n">
         <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.3</v>
@@ -2049,64 +2049,64 @@
         <v>1.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AM8" t="n">
         <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF8" t="n">
         <v>1.36</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.86</v>
+        <v>3.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>3.98</v>
+        <v>3.15</v>
       </c>
       <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2386,13 +2386,13 @@
         <v>4.05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="V10" t="n">
         <v>1.38</v>
@@ -2401,13 +2401,13 @@
         <v>2.77</v>
       </c>
       <c r="X10" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.04</v>
@@ -2416,34 +2416,34 @@
         <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD10" t="n">
         <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
         <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.1</v>
       </c>
       <c r="AK10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL10" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.91</v>
       </c>
       <c r="AM10" t="n">
         <v>1.29</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="X13" t="n">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="S18" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,40 +4150,40 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
         <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="X19" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
@@ -4192,13 +4192,13 @@
         <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
         <v>2.5</v>
@@ -4213,16 +4213,16 @@
         <v>1.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>1.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
         <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF19" t="n">
         <v>1.22</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R24" t="n">
-        <v>3.9</v>
+        <v>4.51</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5538,55 +5538,55 @@
         <v>4.9</v>
       </c>
       <c r="S26" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="X26" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.1</v>
       </c>
       <c r="AD26" t="n">
         <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AH26" t="n">
         <v>1.57</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.22</v>
@@ -5595,7 +5595,7 @@
         <v>1.57</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM26" t="n">
         <v>1.17</v>
@@ -5607,40 +5607,40 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>4.39</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.35</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB26" t="n">
         <v>1.15</v>
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,19 +5923,19 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.09</v>
       </c>
       <c r="U28" t="n">
         <v>3.4</v>
@@ -5944,7 +5944,7 @@
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="X28" t="n">
         <v>2.81</v>
@@ -5974,7 +5974,7 @@
         <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -5989,7 +5989,7 @@
         <v>1.73</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AM28" t="n">
         <v>1.33</v>
@@ -6031,10 +6031,10 @@
         <v>1.39</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
@@ -6129,13 +6129,13 @@
         <v>3.83</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
         <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="V29" t="n">
         <v>1.33</v>
@@ -6144,28 +6144,28 @@
         <v>2.99</v>
       </c>
       <c r="X29" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD29" t="n">
         <v>3.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF29" t="n">
         <v>1.95</v>
@@ -6177,7 +6177,7 @@
         <v>1.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.13</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>3.06</v>
+        <v>1.88</v>
       </c>
       <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.7</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.17</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AQ30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA30" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.45</v>
       </c>
       <c r="BB30" t="n">
         <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="BD30" t="n">
         <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="S31" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
         <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
         <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AH31" t="n">
         <v>1.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.34</v>
+        <v>4.85</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.65</v>
+        <v>3.31</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD31" t="n">
         <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF31" t="n">
         <v>1.22</v>
@@ -6720,13 +6720,13 @@
         <v>7.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="T32" t="n">
         <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="V32" t="n">
         <v>1.14</v>
@@ -6741,7 +6741,7 @@
         <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA32" t="n">
         <v>1.18</v>
@@ -6759,7 +6759,7 @@
         <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AG32" t="n">
         <v>1.8</v>
@@ -6768,16 +6768,16 @@
         <v>1.85</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AM32" t="n">
         <v>1.1</v>
@@ -6789,40 +6789,40 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="AU32" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
         <v>1.11</v>
@@ -6911,16 +6911,16 @@
         <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
         <v>3.32</v>
@@ -6932,10 +6932,10 @@
         <v>2.89</v>
       </c>
       <c r="X33" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
         <v>6.15</v>
@@ -6953,13 +6953,13 @@
         <v>3.8</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH33" t="n">
         <v>1.36</v>
@@ -6974,7 +6974,7 @@
         <v>1.6</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AM33" t="n">
         <v>1.3</v>
@@ -7004,7 +7004,7 @@
         <v>3.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AW33" t="n">
         <v>1.9</v>
@@ -7016,16 +7016,16 @@
         <v>1.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BA33" t="n">
         <v>2.38</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BD33" t="n">
         <v>4</v>
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q34" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W34" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="X34" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AB34" t="n">
         <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AD34" t="n">
-        <v>6.75</v>
+        <v>6.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AN34" t="n">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>14.25</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46156.6875</v>
+        <v>46156.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46156.79166666666</v>
+        <v>46156.6875</v>
       </c>
     </row>
     <row r="36">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46156.875</v>
+        <v>46156.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,597 +7831,6 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="3" t="n">
-        <v>46156.875</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="3" t="n">
         <v>46156.875</v>
       </c>
     </row>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,49 +1786,49 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>3.61</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB7" t="n">
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.4</v>
@@ -1837,79 +1837,79 @@
         <v>2.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AM7" t="n">
         <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AX7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA7" t="n">
         <v>2.67</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.13</v>
       </c>
       <c r="BB7" t="n">
         <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BF7" t="n">
         <v>1.36</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,49 +1983,49 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>3.61</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
         <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AE8" t="n">
         <v>1.4</v>
@@ -2034,79 +2034,79 @@
         <v>2.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AM8" t="n">
         <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AS8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW8" t="n">
         <v>2.08</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AX8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="BB8" t="n">
         <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BF8" t="n">
         <v>1.36</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AG12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV12" t="n">
         <v>3.1</v>
       </c>
-      <c r="R12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AW12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="BC12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.75</v>
       </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
         <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
         <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AJ14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD14" t="n">
         <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
         <v>1.22</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="X15" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
         <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
         <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF15" t="n">
         <v>1.22</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.85</v>
+        <v>4.51</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,40 +4150,40 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>4.95</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="X19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
@@ -4192,13 +4192,13 @@
         <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
         <v>2.5</v>
@@ -4207,64 +4207,64 @@
         <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
       </c>
       <c r="BC19" t="n">
         <v>1.85</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="X21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG21" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,130 +6317,130 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="S30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD30" t="n">
         <v>4</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="n">
         <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.17</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.65</v>
+        <v>3.31</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
         <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF30" t="n">
         <v>1.22</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="R31" t="n">
-        <v>3.5</v>
+        <v>7.9</v>
       </c>
       <c r="S31" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="X31" t="n">
-        <v>2.57</v>
+        <v>1.92</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.1</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AN31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AQ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AX31" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="U33" t="n">
-        <v>3.32</v>
+        <v>4.34</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>2.89</v>
+        <v>3.88</v>
       </c>
       <c r="X33" t="n">
-        <v>2.59</v>
+        <v>1.93</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.15</v>
+        <v>3.82</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AD33" t="n">
-        <v>3.8</v>
+        <v>6.05</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI33" t="n">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.16</v>
+        <v>2.77</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="BD33" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK34" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="AL34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD34" t="n">
         <v>4</v>
       </c>
-      <c r="R34" t="n">
-        <v>4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE34" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>

--- a/jogos_2026-05-14.xlsx
+++ b/jogos_2026-05-14.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>3.27</v>
       </c>
       <c r="R4" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.15</v>
@@ -1213,7 +1213,7 @@
         <v>4.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>2.69</v>
@@ -1222,13 +1222,13 @@
         <v>2.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
         <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
@@ -1240,13 +1240,13 @@
         <v>3.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
@@ -1258,10 +1258,10 @@
         <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
@@ -1395,76 +1395,76 @@
         <v>2.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,34 +1589,34 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="X6" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
         <v>6.3</v>
@@ -1625,25 +1625,25 @@
         <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
         <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" t="n">
         <v>6.1</v>
@@ -1652,10 +1652,10 @@
         <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AM6" t="n">
         <v>1.23</v>
@@ -1706,13 +1706,13 @@
         <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="BD6" t="n">
         <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
         <v>1.16</v>
@@ -2377,34 +2377,34 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
         <v>4.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X10" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
         <v>7</v>
@@ -2413,37 +2413,37 @@
         <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AE10" t="n">
         <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
         <v>3.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM10" t="n">
         <v>1.29</v>
@@ -2491,16 +2491,16 @@
         <v>3.35</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC10" t="n">
         <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF10" t="n">
         <v>1.15</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>3.9</v>
+        <v>7.08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>4.5</v>
+        <v>8.15</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="X11" t="n">
-        <v>2.77</v>
+        <v>3.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>5.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AM11" t="n">
         <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.15</v>
+        <v>2.79</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>2.71</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.65</v>
+        <v>5.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.31</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD17" t="n">
         <v>3.3</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="B